--- a/trunk/psse_validation/data/IEEE30bus.raw.xlsx
+++ b/trunk/psse_validation/data/IEEE30bus.raw.xlsx
@@ -16,21 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="78">
+  <si>
+    <t>names</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Vm</t>
+  </si>
+  <si>
+    <t>Va(rad)</t>
+  </si>
   <si>
     <t>Va(deg)</t>
   </si>
   <si>
-    <t>Va(rad)</t>
-  </si>
-  <si>
-    <t>Vm</t>
-  </si>
-  <si>
-    <t>names</t>
-  </si>
-  <si>
-    <t>number</t>
+    <t>Vnom</t>
   </si>
   <si>
     <t xml:space="preserve">GLEN LYN    </t>
@@ -105,10 +108,25 @@
     <t xml:space="preserve">BUS 30      </t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Q</t>
+    <t>Pf</t>
+  </si>
+  <si>
+    <t>Qf</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Qt</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>ckt</t>
   </si>
   <si>
     <t>1_2_1</t>
@@ -589,10 +607,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,605 +626,698 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1.05999994277954</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>-5.37824410040052</v>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>-0.0938680675279496</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1.04499991168836</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>-0.0938680675279496</v>
       </c>
       <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>-5.37824410040052</v>
+      </c>
+      <c r="G3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>-7.52866052096518</v>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>-0.131399914355754</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>1.02117763781835</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="E4">
+        <v>-0.131399914355754</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>-7.52866052096518</v>
+      </c>
+      <c r="G4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>-9.2794339077733</v>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>-0.161956674411848</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>1.01230036792654</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="E5">
+        <v>-0.161956674411848</v>
       </c>
       <c r="F5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>-9.2794339077733</v>
+      </c>
+      <c r="G5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>-14.1487693547138</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>-0.246942610345029</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>1.00999999249818</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
+      <c r="E6">
+        <v>-0.246942610345029</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-14.1487693547138</v>
+      </c>
+      <c r="G6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>-11.0550249055259</v>
+      <c r="B7" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>-0.192946583491403</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>1.01062570429387</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="E7">
+        <v>-0.192946583491403</v>
       </c>
       <c r="F7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>-11.0550249055259</v>
+      </c>
+      <c r="G7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>-12.8523203681315</v>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>-0.224315306945025</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>1.00259705029173</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="E8">
+        <v>-0.224315306945025</v>
       </c>
       <c r="F8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>-12.8523203681315</v>
+      </c>
+      <c r="G8">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>-11.7973873228941</v>
+      <c r="B9" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>-0.205903251917542</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>1.00999998129108</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
+      <c r="E9">
+        <v>-0.205903251917542</v>
       </c>
       <c r="F9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>-11.7973873228941</v>
+      </c>
+      <c r="G9">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>-14.0979715291356</v>
+      <c r="B10" t="s">
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>-0.246056021035836</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>1.05113165464091</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
+      <c r="E10">
+        <v>-0.246056021035836</v>
       </c>
       <c r="F10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>-14.0979715291356</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>-15.6881765501459</v>
+      <c r="B11" t="s">
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>-0.27381033443421</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>1.04537889818895</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
+      <c r="E11">
+        <v>-0.27381033443421</v>
       </c>
       <c r="F11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>-15.6881765501459</v>
+      </c>
+      <c r="G11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>-14.0979711670509</v>
+      <c r="B12" t="s">
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>-0.246056014716265</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>1.08199996535957</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
+      <c r="E12">
+        <v>-0.246056014716265</v>
       </c>
       <c r="F12">
+        <v>-14.0979711670509</v>
+      </c>
+      <c r="G12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>-14.932910083206</v>
+      <c r="B13" t="s">
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>-0.260628447856205</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>1.05733885405535</v>
       </c>
-      <c r="E13" t="s">
-        <v>8</v>
+      <c r="E13">
+        <v>-0.260628447856205</v>
       </c>
       <c r="F13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>-14.932910083206</v>
+      </c>
+      <c r="G13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>-14.9329097320047</v>
+      <c r="B14" t="s">
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>-0.260628441726585</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>1.07100002040524</v>
       </c>
-      <c r="E14" t="s">
-        <v>8</v>
+      <c r="E14">
+        <v>-0.260628441726585</v>
       </c>
       <c r="F14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>-14.9329097320047</v>
+      </c>
+      <c r="G14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>-15.824524550964</v>
+      <c r="B15" t="s">
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>-0.276190055976999</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>1.04250773898323</v>
       </c>
-      <c r="E15" t="s">
-        <v>13</v>
+      <c r="E15">
+        <v>-0.276190055976999</v>
       </c>
       <c r="F15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>-15.824524550964</v>
+      </c>
+      <c r="G15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
-        <v>-15.9163654280337</v>
+      <c r="B16" t="s">
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>-0.277792981669785</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>1.03791587573137</v>
       </c>
-      <c r="E16" t="s">
-        <v>14</v>
+      <c r="E16">
+        <v>-0.277792981669785</v>
       </c>
       <c r="F16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>-15.9163654280337</v>
+      </c>
+      <c r="G16">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
-        <v>-15.5154264473964</v>
+      <c r="B17" t="s">
+        <v>16</v>
       </c>
       <c r="C17">
-        <v>-0.270795276358074</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>1.04462582784323</v>
       </c>
-      <c r="E17" t="s">
-        <v>15</v>
+      <c r="E17">
+        <v>-0.270795276358074</v>
       </c>
       <c r="F17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>-15.5154264473964</v>
+      </c>
+      <c r="G17">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
-        <v>-15.8499497416698</v>
+      <c r="B18" t="s">
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>-0.276633809267762</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>1.0401502793489</v>
       </c>
-      <c r="E18" t="s">
-        <v>16</v>
+      <c r="E18">
+        <v>-0.276633809267762</v>
       </c>
       <c r="F18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>-15.8499497416698</v>
+      </c>
+      <c r="G18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>-16.5301908352497</v>
+      <c r="B19" t="s">
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>-0.288506256058098</v>
+        <v>18</v>
       </c>
       <c r="D19">
         <v>1.02839626742803</v>
       </c>
-      <c r="E19" t="s">
-        <v>17</v>
+      <c r="E19">
+        <v>-0.288506256058098</v>
       </c>
       <c r="F19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>-16.5301908352497</v>
+      </c>
+      <c r="G19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
-        <v>-16.7037240564833</v>
+      <c r="B20" t="s">
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>-0.291534982130216</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>1.02589994495438</v>
       </c>
-      <c r="E20" t="s">
-        <v>18</v>
+      <c r="E20">
+        <v>-0.291534982130216</v>
       </c>
       <c r="F20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>-16.7037240564833</v>
+      </c>
+      <c r="G20">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
-        <v>-16.5071948044873</v>
+      <c r="B21" t="s">
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>-0.288104899606405</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>1.029986687839</v>
       </c>
-      <c r="E21" t="s">
-        <v>19</v>
+      <c r="E21">
+        <v>-0.288104899606405</v>
       </c>
       <c r="F21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>-16.5071948044873</v>
+      </c>
+      <c r="G21">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>-16.1306679918998</v>
+      <c r="B22" t="s">
+        <v>21</v>
       </c>
       <c r="C22">
-        <v>-0.281533267004714</v>
+        <v>21</v>
       </c>
       <c r="D22">
         <v>1.03298218678066</v>
       </c>
-      <c r="E22" t="s">
-        <v>20</v>
+      <c r="E22">
+        <v>-0.281533267004714</v>
       </c>
       <c r="F22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>-16.1306679918998</v>
+      </c>
+      <c r="G22">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
-        <v>-16.1164392659243</v>
+      <c r="B23" t="s">
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>-0.281284928888078</v>
+        <v>22</v>
       </c>
       <c r="D23">
         <v>1.03351363328317</v>
       </c>
-      <c r="E23" t="s">
-        <v>21</v>
+      <c r="E23">
+        <v>-0.281284928888078</v>
       </c>
       <c r="F23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>-16.1164392659243</v>
+      </c>
+      <c r="G23">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>-16.3066276825155</v>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>-0.284604342956748</v>
+        <v>23</v>
       </c>
       <c r="D24">
         <v>1.02742897975398</v>
       </c>
-      <c r="E24" t="s">
-        <v>22</v>
+      <c r="E24">
+        <v>-0.284604342956748</v>
       </c>
       <c r="F24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>-16.3066276825155</v>
+      </c>
+      <c r="G24">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
-        <v>-16.4827883407722</v>
+      <c r="B25" t="s">
+        <v>24</v>
       </c>
       <c r="C25">
-        <v>-0.287678926455809</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>1.02184577612474</v>
       </c>
-      <c r="E25" t="s">
-        <v>23</v>
+      <c r="E25">
+        <v>-0.287678926455809</v>
       </c>
       <c r="F25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>-16.4827883407722</v>
+      </c>
+      <c r="G25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
-        <v>-16.0545612086429</v>
+      <c r="B26" t="s">
+        <v>25</v>
       </c>
       <c r="C26">
-        <v>-0.28020495305378</v>
+        <v>25</v>
       </c>
       <c r="D26">
         <v>1.01761861718844</v>
       </c>
-      <c r="E26" t="s">
-        <v>24</v>
+      <c r="E26">
+        <v>-0.28020495305378</v>
       </c>
       <c r="F26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>-16.0545612086429</v>
+      </c>
+      <c r="G26">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
-        <v>-16.4739826028592</v>
+      <c r="B27" t="s">
+        <v>26</v>
       </c>
       <c r="C27">
-        <v>-0.287525237336158</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>0.999946367387374</v>
       </c>
-      <c r="E27" t="s">
-        <v>25</v>
+      <c r="E27">
+        <v>-0.287525237336158</v>
       </c>
       <c r="F27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>-16.4739826028592</v>
+      </c>
+      <c r="G27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
-        <v>-15.5300821909876</v>
+      <c r="B28" t="s">
+        <v>27</v>
       </c>
       <c r="C28">
-        <v>-0.271051067338068</v>
+        <v>27</v>
       </c>
       <c r="D28">
         <v>1.0235384780157</v>
       </c>
-      <c r="E28" t="s">
-        <v>26</v>
+      <c r="E28">
+        <v>-0.271051067338068</v>
       </c>
       <c r="F28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>-15.5300821909876</v>
+      </c>
+      <c r="G28">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
-        <v>-11.6772980784751</v>
+      <c r="B29" t="s">
+        <v>27</v>
       </c>
       <c r="C29">
-        <v>-0.203807299206197</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>1.00710102233856</v>
       </c>
-      <c r="E29" t="s">
-        <v>26</v>
+      <c r="E29">
+        <v>-0.203807299206197</v>
       </c>
       <c r="F29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>-11.6772980784751</v>
+      </c>
+      <c r="G29">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
-        <v>-16.7593152574019</v>
+      <c r="B30" t="s">
+        <v>28</v>
       </c>
       <c r="C30">
-        <v>-0.292505231621384</v>
+        <v>29</v>
       </c>
       <c r="D30">
         <v>1.0037057741359</v>
       </c>
-      <c r="E30" t="s">
-        <v>27</v>
+      <c r="E30">
+        <v>-0.292505231621384</v>
       </c>
       <c r="F30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>-16.7593152574019</v>
+      </c>
+      <c r="G30">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
-        <v>-17.6416158222648</v>
+      <c r="B31" t="s">
+        <v>29</v>
       </c>
       <c r="C31">
-        <v>-0.307904281470447</v>
+        <v>30</v>
       </c>
       <c r="D31">
         <v>0.992234779674377</v>
       </c>
-      <c r="E31" t="s">
-        <v>28</v>
+      <c r="E31">
+        <v>-0.307904281470447</v>
       </c>
       <c r="F31">
-        <v>30</v>
+        <v>-17.6416158222648</v>
+      </c>
+      <c r="G31">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1216,536 +1327,1106 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
         <v>173.307144165039</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>-24.7027912139893</v>
       </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-168.093984603882</v>
+      </c>
+      <c r="F2">
+        <v>40.3151178359985</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3">
         <v>87.6497955322266</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>4.28486967086792</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-84.5418949127197</v>
+      </c>
+      <c r="F3">
+        <v>7.07409429550171</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
         <v>43.6526908874512</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>4.74956703186035</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>-42.6342097520828</v>
+      </c>
+      <c r="F4">
+        <v>-1.64587950706482</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5">
         <v>82.3613128662109</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>2.78163409233093</v>
       </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>-79.4182820320129</v>
+      </c>
+      <c r="F5">
+        <v>9.58283448219299</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6">
         <v>60.3799743652344</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1.37238574028015</v>
       </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>-58.4340943098068</v>
+      </c>
+      <c r="F6">
+        <v>4.53223872184753</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7">
         <v>82.1418991088867</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-3.85462784767151</v>
       </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>-81.2863368988037</v>
+      </c>
+      <c r="F7">
+        <v>6.31112813949585</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8">
         <v>72.127326965332</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>-15.9120197296143</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>-71.4954779148102</v>
+      </c>
+      <c r="F8">
+        <v>18.11021733284</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9">
         <v>-14.7817115783691</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>11.4903240203857</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>14.9510474205017</v>
+      </c>
+      <c r="F9">
+        <v>-11.0633032619953</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
         <v>38.1321144104004</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>-2.78136515617371</v>
       </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-37.7510448694229</v>
+      </c>
+      <c r="F10">
+        <v>3.95169103145599</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11">
         <v>29.5630569458008</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>-7.19653463363647</v>
       </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>-29.4550413638353</v>
+      </c>
+      <c r="F11">
+        <v>7.57458913326263</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
         <v>18.6734981536865</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.114676266908646</v>
       </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>-18.6157003045082</v>
+      </c>
+      <c r="F12">
+        <v>0.0901812165975571</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12">
+        <v>28</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
         <v>-0.544959127902985</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>-0.544621825218201</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>0.546817879891023</v>
+      </c>
+      <c r="F13">
+        <v>0.550466956570745</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13">
+        <v>28</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14">
         <v>27.7212467193604</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>5.88191223144531</v>
       </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>-27.7212467193604</v>
+      </c>
+      <c r="F14">
+        <v>-5.08239328861237</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
         <v>-1.52655665885959e-14</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>-15.5993537902832</v>
       </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>1.52655665885959e-14</v>
+      </c>
+      <c r="F15">
+        <v>16.0574558973312</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>11</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16">
         <v>5.33167028427124</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>4.42940664291382</v>
       </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>-5.31742543168366</v>
+      </c>
+      <c r="F16">
+        <v>-4.39225571975112</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17">
         <v>9.02535057067871</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>3.70956254005432</v>
       </c>
-      <c r="D17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>-8.94379631429911</v>
+      </c>
+      <c r="F17">
+        <v>-3.5274595618248</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18">
         <v>15.785590171814</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>10.0108547210693</v>
       </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>-15.6743255183101</v>
+      </c>
+      <c r="F18">
+        <v>-9.77137993276119</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>21</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19">
         <v>7.61829519271851</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>4.60002613067627</v>
       </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>-7.56560803204775</v>
+      </c>
+      <c r="F19">
+        <v>-4.49139057844877</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>22</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20">
         <v>-3.60822483003176e-14</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>-10.3174180984497</v>
       </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>3.60822483003176e-14</v>
+      </c>
+      <c r="F20">
+        <v>10.4507216215134</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>13</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21">
         <v>7.85752010345459</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2.40030479431152</v>
       </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>-7.78319307416677</v>
+      </c>
+      <c r="F21">
+        <v>-2.24579393863678</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>14</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22">
         <v>17.8917655944824</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>6.7899169921875</v>
       </c>
-      <c r="D22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>-17.674910530448</v>
+      </c>
+      <c r="F22">
+        <v>-6.36275839805603</v>
+      </c>
+      <c r="G22">
+        <v>12</v>
+      </c>
+      <c r="H22">
+        <v>15</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23">
         <v>7.24393796920776</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>3.3485643863678</v>
       </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23">
+        <v>-7.19010384008288</v>
+      </c>
+      <c r="F23">
+        <v>-3.23537028580904</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>16</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24">
         <v>1.58319270610809</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>0.645794153213501</v>
       </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24">
+        <v>-1.57724781241268</v>
+      </c>
+      <c r="F24">
+        <v>-0.640422229189426</v>
+      </c>
+      <c r="G24">
+        <v>14</v>
+      </c>
+      <c r="H24">
+        <v>15</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25">
         <v>6.0168285369873</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>1.59529912471771</v>
       </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25">
+        <v>-5.9782348908484</v>
+      </c>
+      <c r="F25">
+        <v>-1.51670908182859</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+      <c r="H25">
+        <v>18</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26">
         <v>5.03532981872559</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>2.90788221359253</v>
       </c>
-      <c r="D26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26">
+        <v>-5.00394460186362</v>
+      </c>
+      <c r="F26">
+        <v>-2.84448408335447</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26">
+        <v>23</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27">
         <v>3.69010376930237</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>1.43537056446075</v>
       </c>
-      <c r="D27" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27">
+        <v>-3.68257581396028</v>
+      </c>
+      <c r="F27">
+        <v>-1.40774411708117</v>
+      </c>
+      <c r="G27">
+        <v>16</v>
+      </c>
+      <c r="H27">
+        <v>17</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28">
         <v>2.7782347202301</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>0.616709232330322</v>
       </c>
-      <c r="D28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>-2.77334136376157</v>
+      </c>
+      <c r="F28">
+        <v>-0.606815310195088</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28">
+        <v>19</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29">
         <v>-6.72665929794312</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>-2.79318451881409</v>
       </c>
-      <c r="D29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29">
+        <v>6.74379700794816</v>
+      </c>
+      <c r="F29">
+        <v>2.82745993882418</v>
+      </c>
+      <c r="G29">
+        <v>19</v>
+      </c>
+      <c r="H29">
+        <v>20</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30">
         <v>-1.8256756067276</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>-1.42861878871918</v>
       </c>
-      <c r="D30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30">
+        <v>1.8262598227011</v>
+      </c>
+      <c r="F30">
+        <v>1.4298073661048</v>
+      </c>
+      <c r="G30">
+        <v>21</v>
+      </c>
+      <c r="H30">
+        <v>22</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31">
         <v>5.73934841156006</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>3.06158328056335</v>
       </c>
-      <c r="D31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31">
+        <v>-5.693792629987</v>
+      </c>
+      <c r="F31">
+        <v>-2.99067471921444</v>
+      </c>
+      <c r="G31">
+        <v>22</v>
+      </c>
+      <c r="H31">
+        <v>24</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32">
         <v>1.80394411087036</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>1.24448418617249</v>
       </c>
-      <c r="D32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32">
+        <v>-1.79793820111081</v>
+      </c>
+      <c r="F32">
+        <v>-1.23219936899841</v>
+      </c>
+      <c r="G32">
+        <v>23</v>
+      </c>
+      <c r="H32">
+        <v>24</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33">
         <v>-1.20826947689056</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>2.01279997825623</v>
       </c>
-      <c r="D33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>1.21821879129857</v>
+      </c>
+      <c r="F33">
+        <v>-1.99542430974543</v>
+      </c>
+      <c r="G33">
+        <v>24</v>
+      </c>
+      <c r="H33">
+        <v>25</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34">
         <v>3.54462671279907</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>2.36665916442871</v>
       </c>
-      <c r="D34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34">
+        <v>-3.50000016763806</v>
+      </c>
+      <c r="F34">
+        <v>-2.30000002682209</v>
+      </c>
+      <c r="G34">
+        <v>25</v>
+      </c>
+      <c r="H34">
+        <v>26</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35">
         <v>-4.76284599304199</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>-0.371234387159348</v>
       </c>
-      <c r="D35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35">
+        <v>4.78693470545113</v>
+      </c>
+      <c r="F35">
+        <v>0.417229942977428</v>
+      </c>
+      <c r="G35">
+        <v>25</v>
+      </c>
+      <c r="H35">
+        <v>27</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36">
         <v>6.18994617462158</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>1.66878843307495</v>
       </c>
-      <c r="D36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36">
+        <v>-6.1037150323391</v>
+      </c>
+      <c r="F36">
+        <v>-1.50585941970348</v>
+      </c>
+      <c r="G36">
+        <v>27</v>
+      </c>
+      <c r="H36">
+        <v>29</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37">
         <v>7.0920033454895</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>1.66277551651001</v>
       </c>
-      <c r="D37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37">
+        <v>-6.92982564866543</v>
+      </c>
+      <c r="F37">
+        <v>-1.35751473903656</v>
+      </c>
+      <c r="G37">
+        <v>27</v>
+      </c>
+      <c r="H37">
+        <v>30</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38">
         <v>3.70371460914612</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>0.605859696865082</v>
       </c>
-      <c r="D38" t="s">
-        <v>67</v>
+      <c r="E38">
+        <v>-3.67017477750778</v>
+      </c>
+      <c r="F38">
+        <v>-0.542484924197197</v>
+      </c>
+      <c r="G38">
+        <v>29</v>
+      </c>
+      <c r="H38">
+        <v>30</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1755,74 +2436,149 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2">
         <v>44.1932220458984</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>14.4100160598755</v>
       </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-44.1932220458984</v>
+      </c>
+      <c r="F2">
+        <v>-9.72139310836792</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
         <v>27.7212448120117</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>-8.09298419952393</v>
       </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-27.7212448120117</v>
+      </c>
+      <c r="F3">
+        <v>9.71743869781494</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4">
         <v>15.8396615982056</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.186543717980385</v>
       </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>-15.8396615982056</v>
+      </c>
+      <c r="F4">
+        <v>1.09606336057186</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5">
         <v>-18.0688819885254</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-3.74879360198975</v>
       </c>
-      <c r="D5" t="s">
-        <v>71</v>
+      <c r="E5">
+        <v>18.0688819885254</v>
+      </c>
+      <c r="F5">
+        <v>5.03601241111755</v>
+      </c>
+      <c r="G5">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
